--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/5.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/5.xlsx
@@ -426,13 +426,13 @@
         <v>-14.23817155808381</v>
       </c>
       <c r="E2">
-        <v>-5.928313441155012</v>
+        <v>-5.145059519840332</v>
       </c>
       <c r="F2">
-        <v>-4.040788763614538</v>
+        <v>-3.601797943603148</v>
       </c>
       <c r="G2">
-        <v>-6.396451851097923</v>
+        <v>-6.842150597050003</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.14248817920645</v>
       </c>
       <c r="E3">
-        <v>-5.047389392442898</v>
+        <v>-4.805088862188488</v>
       </c>
       <c r="F3">
-        <v>-4.661555698128849</v>
+        <v>-3.510419907032932</v>
       </c>
       <c r="G3">
-        <v>-7.348220451456232</v>
+        <v>-6.567302485288629</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.37545386780274</v>
       </c>
       <c r="E4">
-        <v>-5.568236358909112</v>
+        <v>-5.896306186868799</v>
       </c>
       <c r="F4">
-        <v>-4.263629535376439</v>
+        <v>-3.63613128734698</v>
       </c>
       <c r="G4">
-        <v>-5.837366920425804</v>
+        <v>-6.489782750941056</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.77343315461291</v>
       </c>
       <c r="E5">
-        <v>-6.326189695942938</v>
+        <v>-6.793940304669217</v>
       </c>
       <c r="F5">
-        <v>-3.932418426510695</v>
+        <v>-3.519691823372467</v>
       </c>
       <c r="G5">
-        <v>-6.522613431054008</v>
+        <v>-6.620420188466236</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-19.27691268232511</v>
       </c>
       <c r="E6">
-        <v>-7.082476554541941</v>
+        <v>-7.980241998088582</v>
       </c>
       <c r="F6">
-        <v>-4.209957954614254</v>
+        <v>-2.934975438227991</v>
       </c>
       <c r="G6">
-        <v>-6.114148390782111</v>
+        <v>-6.630676258546898</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-20.7704007843259</v>
       </c>
       <c r="E7">
-        <v>-8.321453457618528</v>
+        <v>-8.570216120281884</v>
       </c>
       <c r="F7">
-        <v>-4.10457885220192</v>
+        <v>-3.49962793650926</v>
       </c>
       <c r="G7">
-        <v>-6.391409890241612</v>
+        <v>-6.653227694760413</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-22.17020221811391</v>
       </c>
       <c r="E8">
-        <v>-9.840412323167349</v>
+        <v>-8.96220083038583</v>
       </c>
       <c r="F8">
-        <v>-3.978240397763953</v>
+        <v>-3.348324145285722</v>
       </c>
       <c r="G8">
-        <v>-6.446126586914686</v>
+        <v>-6.735176939039532</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-23.36400030940669</v>
       </c>
       <c r="E9">
-        <v>-9.877505053764178</v>
+        <v>-9.557138160091538</v>
       </c>
       <c r="F9">
-        <v>-3.808567559383336</v>
+        <v>-2.866784233629536</v>
       </c>
       <c r="G9">
-        <v>-6.293020476814473</v>
+        <v>-6.107851733166417</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-24.26092430499393</v>
       </c>
       <c r="E10">
-        <v>-10.44525795400184</v>
+        <v>-9.55627775003008</v>
       </c>
       <c r="F10">
-        <v>-3.891415068439523</v>
+        <v>-3.1574931467028</v>
       </c>
       <c r="G10">
-        <v>-5.958754693714261</v>
+        <v>-6.315300448293768</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-24.79289727408903</v>
       </c>
       <c r="E11">
-        <v>-10.86733437388676</v>
+        <v>-11.37014442838042</v>
       </c>
       <c r="F11">
-        <v>-4.029460011013852</v>
+        <v>-2.667750741024093</v>
       </c>
       <c r="G11">
-        <v>-4.974913528171492</v>
+        <v>-6.32033247751346</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-24.91526569459216</v>
       </c>
       <c r="E12">
-        <v>-11.83722029447956</v>
+        <v>-11.95560819046208</v>
       </c>
       <c r="F12">
-        <v>-3.72997537367533</v>
+        <v>-2.678606495837781</v>
       </c>
       <c r="G12">
-        <v>-5.387698830372138</v>
+        <v>-5.963968802938613</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-24.59569748269896</v>
       </c>
       <c r="E13">
-        <v>-12.26751136621439</v>
+        <v>-12.96779005828652</v>
       </c>
       <c r="F13">
-        <v>-3.471418712974326</v>
+        <v>-2.517559447222515</v>
       </c>
       <c r="G13">
-        <v>-5.689511335550875</v>
+        <v>-5.547273746456088</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-23.83728799921214</v>
       </c>
       <c r="E14">
-        <v>-12.49423847435642</v>
+        <v>-13.43275565549808</v>
       </c>
       <c r="F14">
-        <v>-3.19185879677534</v>
+        <v>-2.217465131475532</v>
       </c>
       <c r="G14">
-        <v>-4.563356438365917</v>
+        <v>-5.004920312939446</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-22.6715445595084</v>
       </c>
       <c r="E15">
-        <v>-13.72663550469986</v>
+        <v>-14.06945910097654</v>
       </c>
       <c r="F15">
-        <v>-3.077822426636349</v>
+        <v>-2.281176525159648</v>
       </c>
       <c r="G15">
-        <v>-5.096013283998032</v>
+        <v>-4.524556844645658</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-21.14963041045105</v>
       </c>
       <c r="E16">
-        <v>-14.73019062953969</v>
+        <v>-14.85680223432014</v>
       </c>
       <c r="F16">
-        <v>-2.636816188733949</v>
+        <v>-1.923509018183294</v>
       </c>
       <c r="G16">
-        <v>-5.013547594614788</v>
+        <v>-4.322544045293791</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-19.34485800701851</v>
       </c>
       <c r="E17">
-        <v>-15.44813942718975</v>
+        <v>-15.81701533443256</v>
       </c>
       <c r="F17">
-        <v>-2.443449557531057</v>
+        <v>-1.917688080443822</v>
       </c>
       <c r="G17">
-        <v>-3.765452063036314</v>
+        <v>-3.771291865367588</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-17.35842754698038</v>
       </c>
       <c r="E18">
-        <v>-15.39340376185904</v>
+        <v>-17.11125320582475</v>
       </c>
       <c r="F18">
-        <v>-1.959592702249241</v>
+        <v>-1.186940462594627</v>
       </c>
       <c r="G18">
-        <v>-3.771609677739359</v>
+        <v>-3.259776163549258</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.30328659931066</v>
       </c>
       <c r="E19">
-        <v>-16.97293549573446</v>
+        <v>-17.50903436265851</v>
       </c>
       <c r="F19">
-        <v>-1.75381050041319</v>
+        <v>-0.9145061627945228</v>
       </c>
       <c r="G19">
-        <v>-3.200298902390712</v>
+        <v>-3.104753247581806</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.28453282207063</v>
       </c>
       <c r="E20">
-        <v>-17.95899259700865</v>
+        <v>-18.34564729320557</v>
       </c>
       <c r="F20">
-        <v>-1.596428977555312</v>
+        <v>-0.760321309744048</v>
       </c>
       <c r="G20">
-        <v>-2.733995321002208</v>
+        <v>-2.973854276959023</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.41824357710383</v>
       </c>
       <c r="E21">
-        <v>-18.9893064747598</v>
+        <v>-19.13607884582241</v>
       </c>
       <c r="F21">
-        <v>-1.377714303826756</v>
+        <v>-0.436621008119488</v>
       </c>
       <c r="G21">
-        <v>-3.396521557594394</v>
+        <v>-2.14524790229822</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.806385601581724</v>
       </c>
       <c r="E22">
-        <v>-18.95656560768435</v>
+        <v>-19.36494339369606</v>
       </c>
       <c r="F22">
-        <v>-1.037415176184899</v>
+        <v>-0.3183086054472458</v>
       </c>
       <c r="G22">
-        <v>-2.446828669289208</v>
+        <v>-2.353719575997205</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.519246899874721</v>
       </c>
       <c r="E23">
-        <v>-20.13450320961154</v>
+        <v>-19.95248119687324</v>
       </c>
       <c r="F23">
-        <v>-0.8903551111659032</v>
+        <v>0.009288336440083105</v>
       </c>
       <c r="G23">
-        <v>-2.122573975899752</v>
+        <v>-2.486826680494682</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.599612901034606</v>
       </c>
       <c r="E24">
-        <v>-20.32029291272424</v>
+        <v>-21.45661836699495</v>
       </c>
       <c r="F24">
-        <v>-0.5852831356954984</v>
+        <v>0.3316110630737875</v>
       </c>
       <c r="G24">
-        <v>-2.234897475501684</v>
+        <v>-1.98912919575727</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.071019627530766</v>
       </c>
       <c r="E25">
-        <v>-20.73625136422479</v>
+        <v>-21.27204682339032</v>
       </c>
       <c r="F25">
-        <v>-0.3530561328924766</v>
+        <v>0.4705812920370438</v>
       </c>
       <c r="G25">
-        <v>-2.60748282321896</v>
+        <v>-2.635420517024869</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.921556210962544</v>
       </c>
       <c r="E26">
-        <v>-21.70447533485677</v>
+        <v>-21.06736432671763</v>
       </c>
       <c r="F26">
-        <v>-0.195350718380104</v>
+        <v>0.3527435438866057</v>
       </c>
       <c r="G26">
-        <v>-2.531015842352874</v>
+        <v>-2.961764164649605</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.104938519227447</v>
       </c>
       <c r="E27">
-        <v>-22.08198704203221</v>
+        <v>-21.42841050240117</v>
       </c>
       <c r="F27">
-        <v>-0.1961699737414727</v>
+        <v>0.4656359386423308</v>
       </c>
       <c r="G27">
-        <v>-3.155868070708153</v>
+        <v>-2.805536210105859</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.572405850636064</v>
       </c>
       <c r="E28">
-        <v>-21.75699204792373</v>
+        <v>-21.82644978225337</v>
       </c>
       <c r="F28">
-        <v>-0.2757388046173792</v>
+        <v>0.6299094782915007</v>
       </c>
       <c r="G28">
-        <v>-4.05990853602679</v>
+        <v>-3.080056577858843</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.266591337685345</v>
       </c>
       <c r="E29">
-        <v>-21.40173326202199</v>
+        <v>-21.45822597526767</v>
       </c>
       <c r="F29">
-        <v>-0.3714864792373628</v>
+        <v>0.5347573998341298</v>
       </c>
       <c r="G29">
-        <v>-3.443918638080139</v>
+        <v>-3.0027586500624</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.115936183808468</v>
       </c>
       <c r="E30">
-        <v>-21.70644974952412</v>
+        <v>-21.49228915675337</v>
       </c>
       <c r="F30">
-        <v>-0.03116167220601955</v>
+        <v>0.519937078630644</v>
       </c>
       <c r="G30">
-        <v>-3.909430999084757</v>
+        <v>-3.86040513019369</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.05144942049905</v>
       </c>
       <c r="E31">
-        <v>-21.32419673006266</v>
+        <v>-21.31120906660866</v>
       </c>
       <c r="F31">
-        <v>-0.2441382449353836</v>
+        <v>0.4771552157456607</v>
       </c>
       <c r="G31">
-        <v>-4.005830774642795</v>
+        <v>-2.835400641415624</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.02282805222484</v>
       </c>
       <c r="E32">
-        <v>-20.4670969831049</v>
+        <v>-21.58635914731471</v>
       </c>
       <c r="F32">
-        <v>-0.5575435964779514</v>
+        <v>0.4124365272997409</v>
       </c>
       <c r="G32">
-        <v>-4.096076246043327</v>
+        <v>-3.080612749509441</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.98616567063795</v>
       </c>
       <c r="E33">
-        <v>-20.17395527516637</v>
+        <v>-20.85772767948055</v>
       </c>
       <c r="F33">
-        <v>-0.2745492690269591</v>
+        <v>0.2026715349910305</v>
       </c>
       <c r="G33">
-        <v>-3.600434610085802</v>
+        <v>-3.604059657451304</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.90409299231369</v>
       </c>
       <c r="E34">
-        <v>-19.70954215178374</v>
+        <v>-21.04953572454943</v>
       </c>
       <c r="F34">
-        <v>-0.3113528043659383</v>
+        <v>0.02231027201209133</v>
       </c>
       <c r="G34">
-        <v>-3.235115909827227</v>
+        <v>-2.793869847625467</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-13.7560843726302</v>
       </c>
       <c r="E35">
-        <v>-20.38161750773611</v>
+        <v>-20.19311524869282</v>
       </c>
       <c r="F35">
-        <v>-0.430824093034697</v>
+        <v>-0.02821599772166451</v>
       </c>
       <c r="G35">
-        <v>-3.672816377756428</v>
+        <v>-3.352918362296653</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-14.53658630782592</v>
       </c>
       <c r="E36">
-        <v>-19.23076470884879</v>
+        <v>-20.01553566895604</v>
       </c>
       <c r="F36">
-        <v>-0.8557227267896614</v>
+        <v>-0.04361037753529053</v>
       </c>
       <c r="G36">
-        <v>-3.218556561039792</v>
+        <v>-3.281102697913243</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-15.23751604812534</v>
       </c>
       <c r="E37">
-        <v>-19.20592602891671</v>
+        <v>-19.6443955247094</v>
       </c>
       <c r="F37">
-        <v>-0.7529364143480903</v>
+        <v>0.07520235904824256</v>
       </c>
       <c r="G37">
-        <v>-4.007462873593655</v>
+        <v>-3.139179610644687</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-15.85250625952654</v>
       </c>
       <c r="E38">
-        <v>-19.54384981631709</v>
+        <v>-18.86331074244439</v>
       </c>
       <c r="F38">
-        <v>-1.091997132722762</v>
+        <v>-0.3868419257830573</v>
       </c>
       <c r="G38">
-        <v>-3.174648795552439</v>
+        <v>-3.06090507191416</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-16.38679437137411</v>
       </c>
       <c r="E39">
-        <v>-18.18731825647539</v>
+        <v>-19.01335720021454</v>
       </c>
       <c r="F39">
-        <v>-0.6034914795764343</v>
+        <v>-0.1723395002977365</v>
       </c>
       <c r="G39">
-        <v>-3.513453336586991</v>
+        <v>-2.196918897075165</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-16.84009831428181</v>
       </c>
       <c r="E40">
-        <v>-17.508735483374</v>
+        <v>-18.52393331488755</v>
       </c>
       <c r="F40">
-        <v>-0.6652827176208607</v>
+        <v>-0.4026786537897782</v>
       </c>
       <c r="G40">
-        <v>-2.778161309041625</v>
+        <v>-2.543546257219015</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-17.2024988877362</v>
       </c>
       <c r="E41">
-        <v>-17.98511283508489</v>
+        <v>-17.96509697997099</v>
       </c>
       <c r="F41">
-        <v>-1.091602001471626</v>
+        <v>-0.2978205944738056</v>
       </c>
       <c r="G41">
-        <v>-2.200636639715766</v>
+        <v>-1.871422749108482</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-17.46714054478035</v>
       </c>
       <c r="E42">
-        <v>-18.23162031769243</v>
+        <v>-16.50721364336362</v>
       </c>
       <c r="F42">
-        <v>-1.027084606304587</v>
+        <v>-0.4001189985151278</v>
       </c>
       <c r="G42">
-        <v>-2.464599677744015</v>
+        <v>-1.986414548415067</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-17.62928494087049</v>
       </c>
       <c r="E43">
-        <v>-16.28086692703823</v>
+        <v>-17.52904568929841</v>
       </c>
       <c r="F43">
-        <v>-0.9640922355261011</v>
+        <v>-0.5991027890764026</v>
       </c>
       <c r="G43">
-        <v>-2.383362200755839</v>
+        <v>-1.543625771992007</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-17.67582172273901</v>
       </c>
       <c r="E44">
-        <v>-15.74360877076822</v>
+        <v>-16.24006084775511</v>
       </c>
       <c r="F44">
-        <v>-1.248991808003532</v>
+        <v>-0.6052368496941329</v>
       </c>
       <c r="G44">
-        <v>-1.656435921788212</v>
+        <v>-2.242620978244803</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-17.59696890155691</v>
       </c>
       <c r="E45">
-        <v>-15.81804782650631</v>
+        <v>-15.74061092097514</v>
       </c>
       <c r="F45">
-        <v>-1.54285597251406</v>
+        <v>-0.5573141387073759</v>
       </c>
       <c r="G45">
-        <v>-2.175354003432352</v>
+        <v>-1.710397814078332</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-17.39742963439282</v>
       </c>
       <c r="E46">
-        <v>-15.817866687546</v>
+        <v>-15.74903841110342</v>
       </c>
       <c r="F46">
-        <v>-1.415172249413947</v>
+        <v>-0.914806860161739</v>
       </c>
       <c r="G46">
-        <v>-1.9048658801462</v>
+        <v>-0.9691832205632096</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-17.08249412101441</v>
       </c>
       <c r="E47">
-        <v>-14.93635393721289</v>
+        <v>-15.77165813877173</v>
       </c>
       <c r="F47">
-        <v>-1.600543478445017</v>
+        <v>-0.8206479942203248</v>
       </c>
       <c r="G47">
-        <v>-2.394022157392293</v>
+        <v>-1.508812075101031</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-16.65638115717218</v>
       </c>
       <c r="E48">
-        <v>-13.85682913242038</v>
+        <v>-14.39909578094288</v>
       </c>
       <c r="F48">
-        <v>-1.412254739421287</v>
+        <v>-0.9678207172061017</v>
       </c>
       <c r="G48">
-        <v>-1.583395355555271</v>
+        <v>-1.446239453863266</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-16.14016118104962</v>
       </c>
       <c r="E49">
-        <v>-12.62233089013738</v>
+        <v>-14.1902923729232</v>
       </c>
       <c r="F49">
-        <v>-1.776187189065013</v>
+        <v>-0.9375380900619602</v>
       </c>
       <c r="G49">
-        <v>-2.374072809972644</v>
+        <v>-1.008595265208233</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-15.56180555880739</v>
       </c>
       <c r="E50">
-        <v>-12.62030213378194</v>
+        <v>-13.67628340220857</v>
       </c>
       <c r="F50">
-        <v>-1.869267520647983</v>
+        <v>-1.300300884932934</v>
       </c>
       <c r="G50">
-        <v>-1.087492186500144</v>
+        <v>-0.9521372215815022</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-14.94492378921559</v>
       </c>
       <c r="E51">
-        <v>-11.91547685380611</v>
+        <v>-12.94098602063512</v>
       </c>
       <c r="F51">
-        <v>-1.542446759017077</v>
+        <v>-1.223920440190402</v>
       </c>
       <c r="G51">
-        <v>-2.097516456713008</v>
+        <v>-0.7949161033759743</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-14.31842679907091</v>
       </c>
       <c r="E52">
-        <v>-12.50732576423859</v>
+        <v>-13.16742783491467</v>
       </c>
       <c r="F52">
-        <v>-1.662010824834949</v>
+        <v>-1.314706194067617</v>
       </c>
       <c r="G52">
-        <v>-1.058015089018473</v>
+        <v>-0.8589354330144005</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.7225138721377</v>
       </c>
       <c r="E53">
-        <v>-12.11364740485577</v>
+        <v>-12.60796204211104</v>
       </c>
       <c r="F53">
-        <v>-2.251460501319021</v>
+        <v>-1.534413251944727</v>
       </c>
       <c r="G53">
-        <v>-1.663639668881666</v>
+        <v>-0.9362466029930006</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.19110783996468</v>
       </c>
       <c r="E54">
-        <v>-10.8515979267101</v>
+        <v>-11.28525818310664</v>
       </c>
       <c r="F54">
-        <v>-2.108607714338844</v>
+        <v>-1.105161547488051</v>
       </c>
       <c r="G54">
-        <v>-1.617450937517754</v>
+        <v>-0.9416129973121591</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.74829926004843</v>
       </c>
       <c r="E55">
-        <v>-12.61829601979655</v>
+        <v>-10.57138048358947</v>
       </c>
       <c r="F55">
-        <v>-2.128632667934119</v>
+        <v>-1.710177075838129</v>
       </c>
       <c r="G55">
-        <v>-0.9601057046945279</v>
+        <v>-1.518177608431629</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.42461157948846</v>
       </c>
       <c r="E56">
-        <v>-10.78359836101092</v>
+        <v>-10.78976161413536</v>
       </c>
       <c r="F56">
-        <v>-2.200774356676525</v>
+        <v>-1.639569523525708</v>
       </c>
       <c r="G56">
-        <v>-1.070194586057452</v>
+        <v>-1.13915656018601</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.24388767557245</v>
       </c>
       <c r="E57">
-        <v>-9.729233757805035</v>
+        <v>-10.1976817515285</v>
       </c>
       <c r="F57">
-        <v>-2.246503550780669</v>
+        <v>-2.033088771695224</v>
       </c>
       <c r="G57">
-        <v>-2.130287547006254</v>
+        <v>-0.7913076087381686</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.21095719245183</v>
       </c>
       <c r="E58">
-        <v>-10.11237888664601</v>
+        <v>-10.21144378403781</v>
       </c>
       <c r="F58">
-        <v>-1.910575717923386</v>
+        <v>-2.084856764165776</v>
       </c>
       <c r="G58">
-        <v>-1.5785420957947</v>
+        <v>-1.152676828168394</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.32343851304221</v>
       </c>
       <c r="E59">
-        <v>-9.526050186028881</v>
+        <v>-9.725937028727451</v>
       </c>
       <c r="F59">
-        <v>-2.484624387654609</v>
+        <v>-1.793240788786447</v>
       </c>
       <c r="G59">
-        <v>-1.391684973921616</v>
+        <v>-0.7158768286258747</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.58167973841121</v>
       </c>
       <c r="E60">
-        <v>-9.579490707793399</v>
+        <v>-9.260147249246494</v>
       </c>
       <c r="F60">
-        <v>-2.278440427628201</v>
+        <v>-1.940575871783172</v>
       </c>
       <c r="G60">
-        <v>-1.427124363919514</v>
+        <v>-1.042879274812925</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.97031249959533</v>
       </c>
       <c r="E61">
-        <v>-9.050759668079831</v>
+        <v>-8.904494486106087</v>
       </c>
       <c r="F61">
-        <v>-2.569858423198262</v>
+        <v>-1.802516018595593</v>
       </c>
       <c r="G61">
-        <v>-2.031288993199888</v>
+        <v>-1.570785487596188</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.4616768215044</v>
       </c>
       <c r="E62">
-        <v>-9.430780149855513</v>
+        <v>-8.712627570875101</v>
       </c>
       <c r="F62">
-        <v>-2.626503014569094</v>
+        <v>-1.849641011773454</v>
       </c>
       <c r="G62">
-        <v>-2.715264254341012</v>
+        <v>-0.9792572106392118</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.03514756843312</v>
       </c>
       <c r="E63">
-        <v>-8.79779005306335</v>
+        <v>-7.864344762810275</v>
       </c>
       <c r="F63">
-        <v>-2.523506296807212</v>
+        <v>-1.985559535224797</v>
       </c>
       <c r="G63">
-        <v>-2.476971186424272</v>
+        <v>-1.351564472531189</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.66841831554239</v>
       </c>
       <c r="E64">
-        <v>-8.086602267106736</v>
+        <v>-7.888816636347725</v>
       </c>
       <c r="F64">
-        <v>-2.598242432255187</v>
+        <v>-1.974876080830892</v>
       </c>
       <c r="G64">
-        <v>-2.343648896466743</v>
+        <v>-1.924268987551868</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-15.32569400008388</v>
       </c>
       <c r="E65">
-        <v>-7.614123931516449</v>
+        <v>-8.145241477032059</v>
       </c>
       <c r="F65">
-        <v>-2.633250067064897</v>
+        <v>-2.266771216024964</v>
       </c>
       <c r="G65">
-        <v>-2.518323210755308</v>
+        <v>-2.214219808063396</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.96931844328706</v>
       </c>
       <c r="E66">
-        <v>-7.813630382398374</v>
+        <v>-7.167543938776029</v>
       </c>
       <c r="F66">
-        <v>-2.764776586546597</v>
+        <v>-1.969378206378511</v>
       </c>
       <c r="G66">
-        <v>-2.049728731853629</v>
+        <v>-2.412044767308085</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-16.57242231957158</v>
       </c>
       <c r="E67">
-        <v>-7.219141371619425</v>
+        <v>-7.051067058824739</v>
       </c>
       <c r="F67">
-        <v>-2.844409201712518</v>
+        <v>-2.140396313421275</v>
       </c>
       <c r="G67">
-        <v>-2.422314079570905</v>
+        <v>-2.180842887936464</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-17.10209897150325</v>
       </c>
       <c r="E68">
-        <v>-7.63122797784342</v>
+        <v>-6.832301007988193</v>
       </c>
       <c r="F68">
-        <v>-2.577131488994841</v>
+        <v>-2.071577206331497</v>
       </c>
       <c r="G68">
-        <v>-2.196822891254526</v>
+        <v>-2.087389497908378</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-17.52724583843274</v>
       </c>
       <c r="E69">
-        <v>-7.044188306807088</v>
+        <v>-6.691556035829798</v>
       </c>
       <c r="F69">
-        <v>-2.707861119035048</v>
+        <v>-2.235146633688288</v>
       </c>
       <c r="G69">
-        <v>-3.235499933109782</v>
+        <v>-2.008419744614603</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-17.83717025287717</v>
       </c>
       <c r="E70">
-        <v>-7.26459819370842</v>
+        <v>-6.330206452387742</v>
       </c>
       <c r="F70">
-        <v>-2.372721063577827</v>
+        <v>-2.289135479165746</v>
       </c>
       <c r="G70">
-        <v>-2.872488683092079</v>
+        <v>-2.375416891461589</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-18.03430641319907</v>
       </c>
       <c r="E71">
-        <v>-7.407847411993057</v>
+        <v>-6.80958165389171</v>
       </c>
       <c r="F71">
-        <v>-2.557265581940904</v>
+        <v>-2.474418901252119</v>
       </c>
       <c r="G71">
-        <v>-2.81043581750398</v>
+        <v>-1.969981000358125</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-18.12084491722179</v>
       </c>
       <c r="E72">
-        <v>-6.135898689666622</v>
+        <v>-5.999165945479023</v>
       </c>
       <c r="F72">
-        <v>-3.066636153228945</v>
+        <v>-2.371297928379817</v>
       </c>
       <c r="G72">
-        <v>-2.744509613634933</v>
+        <v>-2.143549592436574</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.10733932111685</v>
       </c>
       <c r="E73">
-        <v>-7.188759839501965</v>
+        <v>-6.457832435345916</v>
       </c>
       <c r="F73">
-        <v>-3.13891369422541</v>
+        <v>-2.483811759232463</v>
       </c>
       <c r="G73">
-        <v>-1.922312455138159</v>
+        <v>-1.648037067755081</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.02156586385678</v>
       </c>
       <c r="E74">
-        <v>-7.367335683520437</v>
+        <v>-7.085927251735786</v>
       </c>
       <c r="F74">
-        <v>-3.437804392136125</v>
+        <v>-2.59595613822346</v>
       </c>
       <c r="G74">
-        <v>-2.257501880443828</v>
+        <v>-1.374099356017008</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-17.88638895007158</v>
       </c>
       <c r="E75">
-        <v>-7.074977401585239</v>
+        <v>-7.555285468734788</v>
       </c>
       <c r="F75">
-        <v>-3.171423801315679</v>
+        <v>-2.6919274720422</v>
       </c>
       <c r="G75">
-        <v>-0.9163138083010487</v>
+        <v>-1.00574819604446</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-17.72094418639716</v>
       </c>
       <c r="E76">
-        <v>-7.272495852377797</v>
+        <v>-7.321797348899304</v>
       </c>
       <c r="F76">
-        <v>-3.435950505888659</v>
+        <v>-2.833025776863248</v>
       </c>
       <c r="G76">
-        <v>-1.854631662133299</v>
+        <v>-0.5765988672431965</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-17.55480619015858</v>
       </c>
       <c r="E77">
-        <v>-7.838075085091779</v>
+        <v>-7.611610628442192</v>
       </c>
       <c r="F77">
-        <v>-3.272057186877375</v>
+        <v>-2.718324227699809</v>
       </c>
       <c r="G77">
-        <v>-1.607919876910192</v>
+        <v>-0.2213574676061626</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-17.41363544098692</v>
       </c>
       <c r="E78">
-        <v>-8.015084077103598</v>
+        <v>-8.182755355711601</v>
       </c>
       <c r="F78">
-        <v>-3.453551656463343</v>
+        <v>-2.966155187269365</v>
       </c>
       <c r="G78">
-        <v>-1.702882875704186</v>
+        <v>-1.070648130796332</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-17.3052746190253</v>
       </c>
       <c r="E79">
-        <v>-10.33848106537498</v>
+        <v>-8.5035116981489</v>
       </c>
       <c r="F79">
-        <v>-3.811610981221221</v>
+        <v>-3.058050125098928</v>
       </c>
       <c r="G79">
-        <v>-0.4776896981663913</v>
+        <v>0.3860746701214719</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-17.23448685721369</v>
       </c>
       <c r="E80">
-        <v>-9.389516694697621</v>
+        <v>-8.283264836311844</v>
       </c>
       <c r="F80">
-        <v>-3.829375320174257</v>
+        <v>-3.200621267162154</v>
       </c>
       <c r="G80">
-        <v>-0.7343033250974581</v>
+        <v>-0.148886315205977</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-17.21092178225368</v>
       </c>
       <c r="E81">
-        <v>-9.0397011345531</v>
+        <v>-9.672867841831563</v>
       </c>
       <c r="F81">
-        <v>-3.754862843925038</v>
+        <v>-2.928727062908675</v>
       </c>
       <c r="G81">
-        <v>-0.1958099876796068</v>
+        <v>-0.09685116041971249</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-17.22725108557775</v>
       </c>
       <c r="E82">
-        <v>-11.07390977269466</v>
+        <v>-10.36162609602819</v>
       </c>
       <c r="F82">
-        <v>-3.8959354693566</v>
+        <v>-3.520350375457693</v>
       </c>
       <c r="G82">
-        <v>-0.528824384565974</v>
+        <v>0.2308133948751925</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-17.26656340916022</v>
       </c>
       <c r="E83">
-        <v>-12.30378897148983</v>
+        <v>-11.07422223740119</v>
       </c>
       <c r="F83">
-        <v>-3.810303817459604</v>
+        <v>-3.403273068583025</v>
       </c>
       <c r="G83">
-        <v>-0.7869707940817234</v>
+        <v>1.169399402896124</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-17.32281766948207</v>
       </c>
       <c r="E84">
-        <v>-12.49464603701711</v>
+        <v>-12.03563538312563</v>
       </c>
       <c r="F84">
-        <v>-4.227524313758019</v>
+        <v>-3.545626350019314</v>
       </c>
       <c r="G84">
-        <v>-0.3043396020935341</v>
+        <v>0.7414716653988517</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-17.38902226286808</v>
       </c>
       <c r="E85">
-        <v>-14.93200207369152</v>
+        <v>-13.21055249288971</v>
       </c>
       <c r="F85">
-        <v>-4.162918283278881</v>
+        <v>-3.830984838037896</v>
       </c>
       <c r="G85">
-        <v>-0.4396382877380083</v>
+        <v>0.8218947481843666</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-17.44835975198022</v>
       </c>
       <c r="E86">
-        <v>-15.17499093199509</v>
+        <v>-14.39512430923815</v>
       </c>
       <c r="F86">
-        <v>-4.657313628659113</v>
+        <v>-4.265602706529907</v>
       </c>
       <c r="G86">
-        <v>-0.9081566240922845</v>
+        <v>0.8497927154438049</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-17.49147242460909</v>
       </c>
       <c r="E87">
-        <v>-15.83694967701432</v>
+        <v>-15.92659534847017</v>
       </c>
       <c r="F87">
-        <v>-4.590774188661839</v>
+        <v>-4.021106754124022</v>
       </c>
       <c r="G87">
-        <v>-0.1655780858149823</v>
+        <v>1.343878394997873</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-17.52250341612465</v>
       </c>
       <c r="E88">
-        <v>-16.85205693904772</v>
+        <v>-16.52403692430212</v>
       </c>
       <c r="F88">
-        <v>-4.570216594826563</v>
+        <v>-4.416693607330926</v>
       </c>
       <c r="G88">
-        <v>-0.2521687149401595</v>
+        <v>1.437136462839142</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-17.53763432231774</v>
       </c>
       <c r="E89">
-        <v>-19.67874400005758</v>
+        <v>-17.61534481846258</v>
       </c>
       <c r="F89">
-        <v>-5.00591879624884</v>
+        <v>-4.561508796688336</v>
       </c>
       <c r="G89">
-        <v>-0.8473253498081764</v>
+        <v>0.8722646985643777</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-17.53300107082725</v>
       </c>
       <c r="E90">
-        <v>-20.23191068551654</v>
+        <v>-19.28665060657745</v>
       </c>
       <c r="F90">
-        <v>-5.033051970527537</v>
+        <v>-4.839180035208938</v>
       </c>
       <c r="G90">
-        <v>-0.5969885172195678</v>
+        <v>0.90023549782568</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-17.52161451152653</v>
       </c>
       <c r="E91">
-        <v>-22.77811312343931</v>
+        <v>-22.16078701823968</v>
       </c>
       <c r="F91">
-        <v>-5.431734432718703</v>
+        <v>-4.824969392413912</v>
       </c>
       <c r="G91">
-        <v>-0.4809141695216415</v>
+        <v>0.6631309157575382</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-17.51832909992354</v>
       </c>
       <c r="E92">
-        <v>-23.48959073173241</v>
+        <v>-23.80625333366678</v>
       </c>
       <c r="F92">
-        <v>-5.258492159199423</v>
+        <v>-4.879377391797187</v>
       </c>
       <c r="G92">
-        <v>-0.03123945837689683</v>
+        <v>0.6775251677622894</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.52851417871575</v>
       </c>
       <c r="E93">
-        <v>-26.02289607568134</v>
+        <v>-26.11386406154742</v>
       </c>
       <c r="F93">
-        <v>-5.190921401785664</v>
+        <v>-5.102276149277284</v>
       </c>
       <c r="G93">
-        <v>-1.279639560144983</v>
+        <v>0.207222447362346</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.56217803539157</v>
       </c>
       <c r="E94">
-        <v>-28.47575307888401</v>
+        <v>-27.02395601134294</v>
       </c>
       <c r="F94">
-        <v>-5.846982586231053</v>
+        <v>-5.203443831813784</v>
       </c>
       <c r="G94">
-        <v>-1.658753303665701</v>
+        <v>0.643509312346278</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.6377485510763</v>
       </c>
       <c r="E95">
-        <v>-30.23216021478802</v>
+        <v>-30.11384251015261</v>
       </c>
       <c r="F95">
-        <v>-5.542164091185905</v>
+        <v>-5.407121152079321</v>
       </c>
       <c r="G95">
-        <v>-2.046759172504903</v>
+        <v>0.02461606596168663</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.75851632251401</v>
       </c>
       <c r="E96">
-        <v>-31.48978084535419</v>
+        <v>-31.93766730284582</v>
       </c>
       <c r="F96">
-        <v>-5.989142029695087</v>
+        <v>-5.513627662526865</v>
       </c>
       <c r="G96">
-        <v>-2.340152960377272</v>
+        <v>-0.5882221926315777</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.91386383285429</v>
       </c>
       <c r="E97">
-        <v>-35.73791966957971</v>
+        <v>-34.46560414085865</v>
       </c>
       <c r="F97">
-        <v>-6.024302912474315</v>
+        <v>-5.925115028030505</v>
       </c>
       <c r="G97">
-        <v>-2.113877172768087</v>
+        <v>-0.7754037479675099</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.10623174970704</v>
       </c>
       <c r="E98">
-        <v>-36.67965433150383</v>
+        <v>-36.42659188277019</v>
       </c>
       <c r="F98">
-        <v>-5.794515451672538</v>
+        <v>-5.88684528238857</v>
       </c>
       <c r="G98">
-        <v>-2.874743164604323</v>
+        <v>-1.40679430376285</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.321519541637</v>
       </c>
       <c r="E99">
-        <v>-40.94999626378895</v>
+        <v>-39.19879913723077</v>
       </c>
       <c r="F99">
-        <v>-6.703099468656939</v>
+        <v>-6.24279806884113</v>
       </c>
       <c r="G99">
-        <v>-2.514161855012444</v>
+        <v>-2.021350735490996</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-18.54949840216144</v>
       </c>
       <c r="E100">
-        <v>-42.00150339989601</v>
+        <v>-41.50494716800694</v>
       </c>
       <c r="F100">
-        <v>-6.226909153688032</v>
+        <v>-6.280496655158833</v>
       </c>
       <c r="G100">
-        <v>-3.300975902785488</v>
+        <v>-2.836433531623876</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-18.76419825955124</v>
       </c>
       <c r="E101">
-        <v>-44.51822773626585</v>
+        <v>-45.1879913062373</v>
       </c>
       <c r="F101">
-        <v>-6.16026036919359</v>
+        <v>-6.190076625489955</v>
       </c>
       <c r="G101">
-        <v>-3.295318180458874</v>
+        <v>-2.967948263716964</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-18.99844699843021</v>
       </c>
       <c r="E102">
-        <v>-47.38965385623449</v>
+        <v>-47.59218306351654</v>
       </c>
       <c r="F102">
-        <v>-6.671065672823279</v>
+        <v>-6.652854015472732</v>
       </c>
       <c r="G102">
-        <v>-3.541205639842702</v>
+        <v>-3.137660070242162</v>
       </c>
     </row>
   </sheetData>
